--- a/branches/feature-careteam/all-profiles.xlsx
+++ b/branches/feature-careteam/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T07:06:47+00:00</t>
+    <t>2026-09-21T07:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/all-profiles.xlsx
+++ b/branches/feature-careteam/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T07:30:27+00:00</t>
+    <t>2026-09-21T07:49:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/all-profiles.xlsx
+++ b/branches/feature-careteam/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T07:49:30+00:00</t>
+    <t>2026-09-21T07:54:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/all-profiles.xlsx
+++ b/branches/feature-careteam/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T07:54:52+00:00</t>
+    <t>2026-09-21T08:04:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/all-profiles.xlsx
+++ b/branches/feature-careteam/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:56:04+00:00</t>
+    <t>2026-10-15T09:21:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -796,10 +796,10 @@
 </t>
   </si>
   <si>
-    <t>Kategori: fast kontakt</t>
-  </si>
-  <si>
-    <t>Anger att resursen beskriver en fast kontakt och skiljer den från andra användningar av CareTeam, till exempel team. Värdet är fast och är alltid koden fast-kontakt.</t>
+    <t>Type of team</t>
+  </si>
+  <si>
+    <t>Identifies what kind of team.  This is to support differentiation between multiple co-existing teams, such as care plan team, episode of care team, longitudinal care team.</t>
   </si>
   <si>
     <t>There may be multiple axis of categorization and one team may serve multiple purposes.</t>
@@ -816,13 +816,10 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Kategori av CareTeam.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/care-team-category</t>
+    <t>Typ av CareTeam enligt Ineras kodverk.</t>
+  </si>
+  <si>
+    <t>https://fhir.inera.se/ig/careteam/ValueSet/typ-av-careteam-vs</t>
   </si>
   <si>
     <t>CareTeam.category.id</t>
@@ -1206,6 +1203,9 @@
   </si>
   <si>
     <t>Används inte för fast kontakt.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Indicates the reason for the care team.</t>
@@ -6276,13 +6276,13 @@
         <v>77</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="Z37" t="s" s="2">
+      <c r="AA37" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AB37" t="s" s="2">
         <v>77</v>
@@ -6320,10 +6320,10 @@
         <v>180</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -6423,10 +6423,10 @@
         <v>180</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -6528,10 +6528,10 @@
         <v>180</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -6554,19 +6554,19 @@
         <v>102</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="O40" t="s" s="2">
+      <c r="P40" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="P40" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="Q40" t="s" s="2">
         <v>77</v>
@@ -6615,7 +6615,7 @@
         <v>77</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>78</v>
@@ -6635,10 +6635,10 @@
         <v>180</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -6738,10 +6738,10 @@
         <v>180</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -6843,10 +6843,10 @@
         <v>180</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="F43" s="2"/>
       <c r="G43" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>83</v>
@@ -6872,16 +6872,16 @@
         <v>97</v>
       </c>
       <c r="M43" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="O43" t="s" s="2">
+      <c r="P43" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="P43" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="Q43" t="s" s="2">
         <v>77</v>
@@ -6930,7 +6930,7 @@
         <v>77</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>78</v>
@@ -6950,10 +6950,10 @@
         <v>180</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
@@ -6979,13 +6979,13 @@
         <v>122</v>
       </c>
       <c r="M44" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P44" s="2"/>
       <c r="Q44" t="s" s="2">
@@ -7035,7 +7035,7 @@
         <v>77</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>78</v>
@@ -7055,10 +7055,10 @@
         <v>180</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="F45" s="2"/>
       <c r="G45" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>83</v>
@@ -7084,14 +7084,14 @@
         <v>125</v>
       </c>
       <c r="M45" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q45" t="s" s="2">
         <v>77</v>
@@ -7140,16 +7140,16 @@
         <v>77</v>
       </c>
       <c r="AG45" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>107</v>
@@ -7160,10 +7160,10 @@
         <v>180</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -7189,14 +7189,14 @@
         <v>122</v>
       </c>
       <c r="M46" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q46" t="s" s="2">
         <v>77</v>
@@ -7245,7 +7245,7 @@
         <v>77</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>78</v>
@@ -7254,7 +7254,7 @@
         <v>83</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>107</v>
@@ -7265,10 +7265,10 @@
         <v>180</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7294,16 +7294,16 @@
         <v>134</v>
       </c>
       <c r="M47" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="O47" t="s" s="2">
+      <c r="P47" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="P47" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="Q47" t="s" s="2">
         <v>77</v>
@@ -7352,7 +7352,7 @@
         <v>77</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>78</v>
@@ -7372,10 +7372,10 @@
         <v>180</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7401,16 +7401,16 @@
         <v>122</v>
       </c>
       <c r="M48" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="O48" t="s" s="2">
+      <c r="P48" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="P48" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="Q48" t="s" s="2">
         <v>77</v>
@@ -7459,7 +7459,7 @@
         <v>77</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>78</v>
@@ -7479,10 +7479,10 @@
         <v>180</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -7508,13 +7508,13 @@
         <v>122</v>
       </c>
       <c r="M49" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P49" s="2"/>
       <c r="Q49" t="s" s="2">
@@ -7564,7 +7564,7 @@
         <v>77</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>78</v>
@@ -7584,14 +7584,14 @@
         <v>180</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" t="s" s="2">
@@ -7610,19 +7610,19 @@
         <v>102</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="O50" t="s" s="2">
+      <c r="P50" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="P50" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="Q50" t="s" s="2">
         <v>77</v>
@@ -7671,7 +7671,7 @@
         <v>77</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>78</v>
@@ -7691,10 +7691,10 @@
         <v>180</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -7720,14 +7720,14 @@
         <v>166</v>
       </c>
       <c r="M51" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q51" t="s" s="2">
         <v>77</v>
@@ -7776,7 +7776,7 @@
         <v>77</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>78</v>
@@ -7796,10 +7796,10 @@
         <v>180</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -7899,10 +7899,10 @@
         <v>180</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -8004,10 +8004,10 @@
         <v>180</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -8030,16 +8030,16 @@
         <v>102</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="P54" s="2"/>
       <c r="Q54" t="s" s="2">
@@ -8089,16 +8089,16 @@
         <v>77</v>
       </c>
       <c r="AG54" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>107</v>
@@ -8109,10 +8109,10 @@
         <v>180</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8135,69 +8135,69 @@
         <v>102</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M55" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="P55" s="2"/>
       <c r="Q55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="R55" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG55" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="S55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>332</v>
-      </c>
       <c r="AH55" t="s" s="2">
         <v>78</v>
       </c>
@@ -8205,7 +8205,7 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>107</v>
@@ -8216,10 +8216,10 @@
         <v>180</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -8242,13 +8242,13 @@
         <v>77</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M56" t="s" s="2">
         <v>183</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" s="2"/>
@@ -8299,7 +8299,7 @@
         <v>77</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>78</v>
@@ -8311,7 +8311,7 @@
         <v>77</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="57">
@@ -8319,10 +8319,10 @@
         <v>180</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -8422,10 +8422,10 @@
         <v>180</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -8523,13 +8523,13 @@
         <v>180</v>
       </c>
       <c r="B59" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="D59" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="D59" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="E59" t="s" s="2">
         <v>77</v>
@@ -8551,13 +8551,13 @@
         <v>77</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" s="2"/>
@@ -8628,14 +8628,14 @@
         <v>180</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" t="s" s="2">
@@ -8657,16 +8657,16 @@
         <v>90</v>
       </c>
       <c r="M60" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>113</v>
       </c>
       <c r="P60" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q60" t="s" s="2">
         <v>77</v>
@@ -8715,7 +8715,7 @@
         <v>77</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>78</v>
@@ -8735,10 +8735,10 @@
         <v>180</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -8764,13 +8764,13 @@
         <v>249</v>
       </c>
       <c r="M61" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P61" s="2"/>
       <c r="Q61" t="s" s="2">
@@ -8799,37 +8799,37 @@
         <v>129</v>
       </c>
       <c r="Z61" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AA61" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AA61" t="s" s="2">
+      <c r="AB61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>107</v>
@@ -8840,10 +8840,10 @@
         <v>180</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -8866,16 +8866,16 @@
         <v>102</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="P62" s="2"/>
       <c r="Q62" t="s" s="2">
@@ -8925,7 +8925,7 @@
         <v>77</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>78</v>
@@ -8934,7 +8934,7 @@
         <v>83</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>107</v>
@@ -8945,10 +8945,10 @@
         <v>180</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -8971,17 +8971,17 @@
         <v>102</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q63" t="s" s="2">
         <v>77</v>
@@ -9030,7 +9030,7 @@
         <v>77</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>78</v>
@@ -9039,7 +9039,7 @@
         <v>83</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>107</v>
@@ -9050,10 +9050,10 @@
         <v>180</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -9076,19 +9076,19 @@
         <v>77</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="O64" t="s" s="2">
+      <c r="P64" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="P64" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="Q64" t="s" s="2">
         <v>77</v>
@@ -9137,7 +9137,7 @@
         <v>77</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>78</v>
@@ -9157,10 +9157,10 @@
         <v>180</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -9183,13 +9183,13 @@
         <v>77</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" s="2"/>
@@ -9216,7 +9216,7 @@
         <v>77</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>255</v>
+        <v>378</v>
       </c>
       <c r="Z65" t="s" s="2">
         <v>379</v>
@@ -9240,7 +9240,7 @@
         <v>77</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>78</v>
@@ -9286,13 +9286,13 @@
         <v>102</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="M66" t="s" s="2">
         <v>382</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -13507,13 +13507,13 @@
         <v>77</v>
       </c>
       <c r="Y106" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="Z106" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="Z106" t="s" s="2">
+      <c r="AA106" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AB106" t="s" s="2">
         <v>77</v>
@@ -13551,10 +13551,10 @@
         <v>467</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -13654,10 +13654,10 @@
         <v>467</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -13759,10 +13759,10 @@
         <v>467</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -13785,19 +13785,19 @@
         <v>102</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="N109" t="s" s="2">
+      <c r="O109" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="O109" t="s" s="2">
+      <c r="P109" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="P109" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="Q109" t="s" s="2">
         <v>77</v>
@@ -13846,7 +13846,7 @@
         <v>77</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>78</v>
@@ -13866,10 +13866,10 @@
         <v>467</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -13969,10 +13969,10 @@
         <v>467</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -14074,10 +14074,10 @@
         <v>467</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="F112" s="2"/>
       <c r="G112" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>83</v>
@@ -14103,16 +14103,16 @@
         <v>97</v>
       </c>
       <c r="M112" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N112" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="N112" t="s" s="2">
+      <c r="O112" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="O112" t="s" s="2">
+      <c r="P112" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="P112" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="Q112" t="s" s="2">
         <v>77</v>
@@ -14161,7 +14161,7 @@
         <v>77</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>78</v>
@@ -14181,10 +14181,10 @@
         <v>467</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -14210,13 +14210,13 @@
         <v>122</v>
       </c>
       <c r="M113" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N113" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N113" t="s" s="2">
+      <c r="O113" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P113" s="2"/>
       <c r="Q113" t="s" s="2">
@@ -14266,7 +14266,7 @@
         <v>77</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>78</v>
@@ -14286,10 +14286,10 @@
         <v>467</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -14297,7 +14297,7 @@
       </c>
       <c r="F114" s="2"/>
       <c r="G114" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>83</v>
@@ -14315,14 +14315,14 @@
         <v>125</v>
       </c>
       <c r="M114" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N114" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q114" t="s" s="2">
         <v>77</v>
@@ -14371,16 +14371,16 @@
         <v>77</v>
       </c>
       <c r="AG114" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>107</v>
@@ -14391,10 +14391,10 @@
         <v>467</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
@@ -14420,14 +14420,14 @@
         <v>122</v>
       </c>
       <c r="M115" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="N115" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q115" t="s" s="2">
         <v>77</v>
@@ -14476,7 +14476,7 @@
         <v>77</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>78</v>
@@ -14485,7 +14485,7 @@
         <v>83</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>107</v>
@@ -14496,10 +14496,10 @@
         <v>467</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -14525,16 +14525,16 @@
         <v>134</v>
       </c>
       <c r="M116" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N116" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="N116" t="s" s="2">
+      <c r="O116" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="O116" t="s" s="2">
+      <c r="P116" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="P116" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="Q116" t="s" s="2">
         <v>77</v>
@@ -14583,7 +14583,7 @@
         <v>77</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>78</v>
@@ -14603,10 +14603,10 @@
         <v>467</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -14632,16 +14632,16 @@
         <v>122</v>
       </c>
       <c r="M117" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="N117" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N117" t="s" s="2">
+      <c r="O117" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="O117" t="s" s="2">
+      <c r="P117" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="P117" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="Q117" t="s" s="2">
         <v>77</v>
@@ -14690,7 +14690,7 @@
         <v>77</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AH117" t="s" s="2">
         <v>78</v>
@@ -14710,10 +14710,10 @@
         <v>467</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
@@ -14745,7 +14745,7 @@
         <v>481</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P118" s="2"/>
       <c r="Q118" t="s" s="2">
@@ -14795,7 +14795,7 @@
         <v>77</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>78</v>
@@ -14815,14 +14815,14 @@
         <v>467</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" t="s" s="2">
@@ -14841,19 +14841,19 @@
         <v>102</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>482</v>
       </c>
       <c r="O119" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="P119" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="P119" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="Q119" t="s" s="2">
         <v>77</v>
@@ -14902,7 +14902,7 @@
         <v>77</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>78</v>
@@ -14922,10 +14922,10 @@
         <v>467</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
@@ -14951,14 +14951,14 @@
         <v>166</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>483</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q120" t="s" s="2">
         <v>77</v>
@@ -15007,7 +15007,7 @@
         <v>77</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AH120" t="s" s="2">
         <v>78</v>
@@ -15027,10 +15027,10 @@
         <v>467</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
@@ -15130,10 +15130,10 @@
         <v>467</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
@@ -15235,10 +15235,10 @@
         <v>467</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -15261,16 +15261,16 @@
         <v>102</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="N123" t="s" s="2">
         <v>484</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P123" s="2"/>
       <c r="Q123" t="s" s="2">
@@ -15320,16 +15320,16 @@
         <v>77</v>
       </c>
       <c r="AG123" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>107</v>
@@ -15340,10 +15340,10 @@
         <v>467</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -15366,69 +15366,69 @@
         <v>102</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="N124" t="s" s="2">
         <v>485</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P124" s="2"/>
       <c r="Q124" t="s" s="2">
         <v>77</v>
       </c>
       <c r="R124" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG124" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="S124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>332</v>
-      </c>
       <c r="AH124" t="s" s="2">
         <v>78</v>
       </c>
@@ -15436,7 +15436,7 @@
         <v>83</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>107</v>
@@ -15447,10 +15447,10 @@
         <v>467</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -15473,7 +15473,7 @@
         <v>77</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M125" t="s" s="2">
         <v>486</v>
@@ -15530,7 +15530,7 @@
         <v>77</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AH125" t="s" s="2">
         <v>78</v>
@@ -15542,7 +15542,7 @@
         <v>77</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="126">
@@ -15550,10 +15550,10 @@
         <v>467</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -15653,10 +15653,10 @@
         <v>467</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -15758,14 +15758,14 @@
         <v>467</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F128" s="2"/>
       <c r="G128" t="s" s="2">
@@ -15787,16 +15787,16 @@
         <v>90</v>
       </c>
       <c r="M128" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="N128" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="O128" t="s" s="2">
         <v>113</v>
       </c>
       <c r="P128" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q128" t="s" s="2">
         <v>77</v>
@@ -15845,7 +15845,7 @@
         <v>77</v>
       </c>
       <c r="AG128" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AH128" t="s" s="2">
         <v>78</v>
@@ -15865,10 +15865,10 @@
         <v>467</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -15900,7 +15900,7 @@
         <v>489</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="P129" s="2"/>
       <c r="Q129" t="s" s="2">
@@ -15926,7 +15926,7 @@
         <v>77</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>255</v>
+        <v>378</v>
       </c>
       <c r="Z129" t="s" s="2">
         <v>490</v>
@@ -15950,7 +15950,7 @@
         <v>77</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>78</v>
@@ -15959,7 +15959,7 @@
         <v>83</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>107</v>
@@ -15970,10 +15970,10 @@
         <v>467</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -16005,7 +16005,7 @@
         <v>494</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P130" s="2"/>
       <c r="Q130" t="s" s="2">
@@ -16055,7 +16055,7 @@
         <v>77</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>78</v>
@@ -16064,7 +16064,7 @@
         <v>83</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>107</v>
@@ -16075,10 +16075,10 @@
         <v>467</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
@@ -16101,17 +16101,17 @@
         <v>102</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N131" t="s" s="2">
         <v>495</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q131" t="s" s="2">
         <v>77</v>
@@ -16160,7 +16160,7 @@
         <v>77</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>78</v>
@@ -16169,7 +16169,7 @@
         <v>83</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>107</v>
@@ -16180,10 +16180,10 @@
         <v>467</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -16206,19 +16206,19 @@
         <v>77</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>496</v>
       </c>
       <c r="O132" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="P132" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="P132" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="Q132" t="s" s="2">
         <v>77</v>
@@ -16267,7 +16267,7 @@
         <v>77</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>78</v>
@@ -16287,10 +16287,10 @@
         <v>467</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
@@ -16313,10 +16313,10 @@
         <v>77</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>497</v>
@@ -16346,7 +16346,7 @@
         <v>77</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>255</v>
+        <v>378</v>
       </c>
       <c r="Z133" t="s" s="2">
         <v>379</v>
@@ -16370,7 +16370,7 @@
         <v>77</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>78</v>
@@ -16416,7 +16416,7 @@
         <v>102</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="M134" t="s" s="2">
         <v>498</v>

--- a/branches/feature-careteam/all-profiles.xlsx
+++ b/branches/feature-careteam/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5525" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5525" uniqueCount="505">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:21:11+00:00</t>
+    <t>2026-10-15T12:03:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1122,6 +1122,9 @@
     <t>Roles may sometimes be inferred by type of Practitioner.  These are relationships that hold only within the context of the care team.  General relationships should be handled as properties of the Patient resource directly.  If a participant has multiple roles within the team, then there should be multiple participants.</t>
   </si>
   <si>
+    <t>extensible</t>
+  </si>
+  <si>
     <t>Typ av fast kontakt.</t>
   </si>
   <si>
@@ -1130,6 +1133,10 @@
   <si>
     <t xml:space="preserve">ctm-2
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+fast-kontakt-typ-kod-eller-text:Typ av fast kontakt ska anges med kod från kodverket Typ av fast kontakt, med text eller med båda. Koder från andra kodverk får inte användas. {(coding.exists() or text.exists()) and coding.all(system = 'https://fhir.inera.se/ig/careteam/CodeSystem/&lt;id&gt;')}</t>
   </si>
   <si>
     <t>CareTeam.participant.member</t>
@@ -2246,7 +2253,7 @@
         <v>2</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="68">
@@ -2254,7 +2261,7 @@
         <v>4</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="69">
@@ -2270,7 +2277,7 @@
         <v>8</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="71">
@@ -2278,7 +2285,7 @@
         <v>10</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="72">
@@ -2332,7 +2339,7 @@
         <v>23</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="79">
@@ -8796,13 +8803,13 @@
         <v>77</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>129</v>
+        <v>353</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA61" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AB61" t="s" s="2">
         <v>77</v>
@@ -8829,10 +8836,10 @@
         <v>83</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>107</v>
+        <v>357</v>
       </c>
     </row>
     <row r="62">
@@ -8840,10 +8847,10 @@
         <v>180</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -8866,16 +8873,16 @@
         <v>102</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="P62" s="2"/>
       <c r="Q62" t="s" s="2">
@@ -8925,7 +8932,7 @@
         <v>77</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>78</v>
@@ -8934,7 +8941,7 @@
         <v>83</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>107</v>
@@ -8945,10 +8952,10 @@
         <v>180</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -8971,17 +8978,17 @@
         <v>102</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q63" t="s" s="2">
         <v>77</v>
@@ -9030,7 +9037,7 @@
         <v>77</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>78</v>
@@ -9039,7 +9046,7 @@
         <v>83</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>107</v>
@@ -9050,10 +9057,10 @@
         <v>180</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -9076,19 +9083,19 @@
         <v>77</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="P64" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q64" t="s" s="2">
         <v>77</v>
@@ -9137,7 +9144,7 @@
         <v>77</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>78</v>
@@ -9157,10 +9164,10 @@
         <v>180</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -9183,13 +9190,13 @@
         <v>77</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" s="2"/>
@@ -9216,13 +9223,13 @@
         <v>77</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AA65" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AB65" t="s" s="2">
         <v>77</v>
@@ -9240,7 +9247,7 @@
         <v>77</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>78</v>
@@ -9260,10 +9267,10 @@
         <v>180</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -9286,17 +9293,17 @@
         <v>102</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q66" t="s" s="2">
         <v>77</v>
@@ -9345,7 +9352,7 @@
         <v>77</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>78</v>
@@ -9365,10 +9372,10 @@
         <v>180</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -9391,16 +9398,16 @@
         <v>77</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P67" s="2"/>
       <c r="Q67" t="s" s="2">
@@ -9450,7 +9457,7 @@
         <v>77</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>78</v>
@@ -9470,10 +9477,10 @@
         <v>180</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -9573,10 +9580,10 @@
         <v>180</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -9678,13 +9685,13 @@
         <v>180</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E70" t="s" s="2">
         <v>77</v>
@@ -9706,13 +9713,13 @@
         <v>77</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" s="2"/>
@@ -9783,10 +9790,10 @@
         <v>180</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -9886,10 +9893,10 @@
         <v>180</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -9989,10 +9996,10 @@
         <v>180</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -10094,10 +10101,10 @@
         <v>180</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -10197,10 +10204,10 @@
         <v>180</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10300,10 +10307,10 @@
         <v>180</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10405,10 +10412,10 @@
         <v>180</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -10510,10 +10517,10 @@
         <v>180</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -10613,10 +10620,10 @@
         <v>180</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -10718,10 +10725,10 @@
         <v>180</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -10823,10 +10830,10 @@
         <v>180</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -10928,10 +10935,10 @@
         <v>180</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -11035,10 +11042,10 @@
         <v>180</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -11142,10 +11149,10 @@
         <v>180</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -11247,10 +11254,10 @@
         <v>180</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -11350,10 +11357,10 @@
         <v>180</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -11455,10 +11462,10 @@
         <v>180</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -11562,10 +11569,10 @@
         <v>180</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -11667,10 +11674,10 @@
         <v>180</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -11696,10 +11703,10 @@
         <v>125</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" s="2"/>
@@ -11729,10 +11736,10 @@
         <v>129</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AA89" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AB89" t="s" s="2">
         <v>77</v>
@@ -11750,7 +11757,7 @@
         <v>77</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>78</v>
@@ -11759,7 +11766,7 @@
         <v>83</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>107</v>
@@ -11770,10 +11777,10 @@
         <v>180</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -11799,16 +11806,16 @@
         <v>122</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="P90" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="Q90" t="s" s="2">
         <v>77</v>
@@ -11857,7 +11864,7 @@
         <v>77</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>78</v>
@@ -11866,7 +11873,7 @@
         <v>83</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>107</v>
@@ -11877,10 +11884,10 @@
         <v>180</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -11906,16 +11913,16 @@
         <v>125</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="P91" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="Q91" t="s" s="2">
         <v>77</v>
@@ -11943,10 +11950,10 @@
         <v>129</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AA91" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AB91" t="s" s="2">
         <v>77</v>
@@ -11964,7 +11971,7 @@
         <v>77</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>78</v>
@@ -11984,10 +11991,10 @@
         <v>180</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -12010,16 +12017,16 @@
         <v>102</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="P92" s="2"/>
       <c r="Q92" t="s" s="2">
@@ -12069,7 +12076,7 @@
         <v>77</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>78</v>
@@ -12089,10 +12096,10 @@
         <v>180</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -12118,10 +12125,10 @@
         <v>166</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" s="2"/>
@@ -12172,7 +12179,7 @@
         <v>77</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>78</v>
@@ -12192,10 +12199,10 @@
         <v>180</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -12218,13 +12225,13 @@
         <v>77</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" s="2"/>
@@ -12275,7 +12282,7 @@
         <v>77</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>78</v>
@@ -12292,7 +12299,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>186</v>
@@ -12324,10 +12331,10 @@
         <v>80</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" s="2"/>
@@ -12395,7 +12402,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>190</v>
@@ -12500,7 +12507,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>195</v>
@@ -12603,7 +12610,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>200</v>
@@ -12708,7 +12715,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>205</v>
@@ -12813,7 +12820,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>212</v>
@@ -12918,7 +12925,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>220</v>
@@ -13023,7 +13030,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>228</v>
@@ -13126,7 +13133,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>232</v>
@@ -13229,7 +13236,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>236</v>
@@ -13261,10 +13268,10 @@
         <v>237</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="O104" t="s" s="2">
         <v>240</v>
@@ -13336,7 +13343,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>242</v>
@@ -13371,7 +13378,7 @@
         <v>243</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O105" t="s" s="2">
         <v>245</v>
@@ -13403,7 +13410,7 @@
         <v>129</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>247</v>
@@ -13441,7 +13448,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>248</v>
@@ -13473,10 +13480,10 @@
         <v>249</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="O106" t="s" s="2">
         <v>252</v>
@@ -13492,7 +13499,7 @@
         <v>77</v>
       </c>
       <c r="T106" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="U106" t="s" s="2">
         <v>77</v>
@@ -13548,7 +13555,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>257</v>
@@ -13651,7 +13658,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>258</v>
@@ -13756,7 +13763,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>259</v>
@@ -13863,7 +13870,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>266</v>
@@ -13966,7 +13973,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>267</v>
@@ -14071,7 +14078,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>268</v>
@@ -14178,7 +14185,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>274</v>
@@ -14283,7 +14290,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>279</v>
@@ -14388,7 +14395,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>285</v>
@@ -14493,7 +14500,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>290</v>
@@ -14600,7 +14607,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>296</v>
@@ -14707,7 +14714,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>302</v>
@@ -14739,10 +14746,10 @@
         <v>122</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="O118" t="s" s="2">
         <v>305</v>
@@ -14812,7 +14819,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>306</v>
@@ -14847,7 +14854,7 @@
         <v>309</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="O119" t="s" s="2">
         <v>311</v>
@@ -14919,7 +14926,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>313</v>
@@ -14954,7 +14961,7 @@
         <v>314</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -15024,7 +15031,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>317</v>
@@ -15127,7 +15134,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>318</v>
@@ -15232,7 +15239,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>319</v>
@@ -15267,7 +15274,7 @@
         <v>321</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="O123" t="s" s="2">
         <v>323</v>
@@ -15337,7 +15344,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>326</v>
@@ -15372,7 +15379,7 @@
         <v>327</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="O124" t="s" s="2">
         <v>329</v>
@@ -15444,7 +15451,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>332</v>
@@ -15476,10 +15483,10 @@
         <v>333</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" s="2"/>
@@ -15547,7 +15554,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>336</v>
@@ -15650,7 +15657,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>337</v>
@@ -15755,7 +15762,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>343</v>
@@ -15862,7 +15869,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>349</v>
@@ -15894,10 +15901,10 @@
         <v>249</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="O129" t="s" s="2">
         <v>352</v>
@@ -15926,13 +15933,13 @@
         <v>77</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AA129" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AB129" t="s" s="2">
         <v>77</v>
@@ -15959,7 +15966,7 @@
         <v>83</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>107</v>
@@ -15967,13 +15974,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -15996,16 +16003,16 @@
         <v>102</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="P130" s="2"/>
       <c r="Q130" t="s" s="2">
@@ -16055,7 +16062,7 @@
         <v>77</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>78</v>
@@ -16064,7 +16071,7 @@
         <v>83</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>107</v>
@@ -16072,13 +16079,13 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
@@ -16101,17 +16108,17 @@
         <v>102</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q131" t="s" s="2">
         <v>77</v>
@@ -16160,7 +16167,7 @@
         <v>77</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>78</v>
@@ -16169,7 +16176,7 @@
         <v>83</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>107</v>
@@ -16177,13 +16184,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -16206,19 +16213,19 @@
         <v>77</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="P132" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q132" t="s" s="2">
         <v>77</v>
@@ -16267,7 +16274,7 @@
         <v>77</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>78</v>
@@ -16284,13 +16291,13 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
@@ -16313,13 +16320,13 @@
         <v>77</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" s="2"/>
@@ -16346,13 +16353,13 @@
         <v>77</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AA133" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AB133" t="s" s="2">
         <v>77</v>
@@ -16370,7 +16377,7 @@
         <v>77</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>78</v>
@@ -16387,13 +16394,13 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
@@ -16416,17 +16423,17 @@
         <v>102</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q134" t="s" s="2">
         <v>77</v>
@@ -16475,7 +16482,7 @@
         <v>77</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>78</v>
@@ -16492,13 +16499,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
@@ -16521,16 +16528,16 @@
         <v>77</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P135" s="2"/>
       <c r="Q135" t="s" s="2">
@@ -16580,7 +16587,7 @@
         <v>77</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AH135" t="s" s="2">
         <v>78</v>
@@ -16597,13 +16604,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
@@ -16700,13 +16707,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
@@ -16805,16 +16812,16 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D138" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E138" t="s" s="2">
         <v>77</v>
@@ -16836,13 +16843,13 @@
         <v>77</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" s="2"/>
@@ -16910,13 +16917,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -17013,13 +17020,13 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
@@ -17116,13 +17123,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
@@ -17221,13 +17228,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -17324,13 +17331,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
@@ -17427,13 +17434,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -17532,13 +17539,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
@@ -17637,13 +17644,13 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
@@ -17740,13 +17747,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
@@ -17845,13 +17852,13 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
@@ -17950,13 +17957,13 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" t="s" s="2">
@@ -18055,13 +18062,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -18162,13 +18169,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
@@ -18269,13 +18276,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
@@ -18374,13 +18381,13 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
@@ -18477,13 +18484,13 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
@@ -18582,13 +18589,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
@@ -18689,13 +18696,13 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
@@ -18794,13 +18801,13 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
@@ -18826,10 +18833,10 @@
         <v>125</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" s="2"/>
@@ -18859,10 +18866,10 @@
         <v>129</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AA157" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AB157" t="s" s="2">
         <v>77</v>
@@ -18880,7 +18887,7 @@
         <v>77</v>
       </c>
       <c r="AG157" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AH157" t="s" s="2">
         <v>78</v>
@@ -18889,7 +18896,7 @@
         <v>83</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>107</v>
@@ -18897,13 +18904,13 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
@@ -18929,16 +18936,16 @@
         <v>122</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="P158" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="Q158" t="s" s="2">
         <v>77</v>
@@ -18987,7 +18994,7 @@
         <v>77</v>
       </c>
       <c r="AG158" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AH158" t="s" s="2">
         <v>78</v>
@@ -18996,7 +19003,7 @@
         <v>83</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>107</v>
@@ -19004,13 +19011,13 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -19036,16 +19043,16 @@
         <v>125</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="P159" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="Q159" t="s" s="2">
         <v>77</v>
@@ -19073,10 +19080,10 @@
         <v>129</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AA159" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AB159" t="s" s="2">
         <v>77</v>
@@ -19094,7 +19101,7 @@
         <v>77</v>
       </c>
       <c r="AG159" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AH159" t="s" s="2">
         <v>78</v>
@@ -19111,13 +19118,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" t="s" s="2">
@@ -19140,16 +19147,16 @@
         <v>102</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="P160" s="2"/>
       <c r="Q160" t="s" s="2">
@@ -19199,7 +19206,7 @@
         <v>77</v>
       </c>
       <c r="AG160" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AH160" t="s" s="2">
         <v>78</v>
@@ -19216,13 +19223,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" t="s" s="2">
@@ -19248,10 +19255,10 @@
         <v>166</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" s="2"/>
@@ -19302,7 +19309,7 @@
         <v>77</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AH161" t="s" s="2">
         <v>78</v>
@@ -19319,13 +19326,13 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" t="s" s="2">
@@ -19348,13 +19355,13 @@
         <v>77</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" s="2"/>
@@ -19405,7 +19412,7 @@
         <v>77</v>
       </c>
       <c r="AG162" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AH162" t="s" s="2">
         <v>78</v>

--- a/branches/feature-careteam/all-profiles.xlsx
+++ b/branches/feature-careteam/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T12:03:42+00:00</t>
+    <t>2026-10-15T12:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1136,7 +1136,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-fast-kontakt-typ-kod-eller-text:Typ av fast kontakt ska anges med kod från kodverket Typ av fast kontakt, med text eller med båda. Koder från andra kodverk får inte användas. {(coding.exists() or text.exists()) and coding.all(system = 'https://fhir.inera.se/ig/careteam/CodeSystem/&lt;id&gt;')}</t>
+fast-kontakt-typ-kod-eller-text:Typ av fast kontakt ska anges med kod från kodverket Typ av fast kontakt, med text eller med båda. Koder från andra kodverk får inte användas. {(coding.exists() or text.exists()) and coding.all(system = 'https://terminologitjansten.inera.se/inera-kodverksforvaltning/kodverk/kv_typ_av_fast_kontakt')}</t>
   </si>
   <si>
     <t>CareTeam.participant.member</t>

--- a/branches/feature-careteam/all-profiles.xlsx
+++ b/branches/feature-careteam/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T12:49:20+00:00</t>
+    <t>2026-10-15T13:32:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/all-profiles.xlsx
+++ b/branches/feature-careteam/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:32:05+00:00</t>
+    <t>2026-10-15T13:47:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/all-profiles.xlsx
+++ b/branches/feature-careteam/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:47:34+00:00</t>
+    <t>2026-10-15T13:54:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/all-profiles.xlsx
+++ b/branches/feature-careteam/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:54:27+00:00</t>
+    <t>2026-10-15T14:04:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
